--- a/resources/data-imports/Monsters/raid-bosses.xlsx
+++ b/resources/data-imports/Monsters/raid-bosses.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="65">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -200,6 +200,9 @@
   </si>
   <si>
     <t xml:space="preserve">Jester of Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delusinal</t>
   </si>
   <si>
     <t xml:space="preserve">Delusional Memories</t>
@@ -221,7 +224,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -242,6 +245,18 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="6.4"/>
+      <color rgb="FF2E3436"/>
+      <name val="Adwaita Sans"/>
       <family val="0"/>
     </font>
   </fonts>
@@ -287,12 +302,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -305,6 +328,66 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF2E3436"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -316,34 +399,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -750,7 +833,7 @@
         <v>1</v>
       </c>
       <c r="W2" s="1" t="n">
-        <v>20000000000000</v>
+        <v>100000000</v>
       </c>
       <c r="X2" s="1" t="n">
         <v>0</v>
@@ -887,7 +970,7 @@
         <v>1</v>
       </c>
       <c r="W3" s="1" t="n">
-        <v>50000000000000</v>
+        <v>250000000</v>
       </c>
       <c r="X3" s="1" t="n">
         <v>0</v>
@@ -1023,8 +1106,8 @@
       <c r="V4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="W4" s="1" t="n">
-        <v>62500000000000</v>
+      <c r="W4" s="2" t="n">
+        <v>250000000</v>
       </c>
       <c r="X4" s="1" t="n">
         <v>0</v>
@@ -1121,8 +1204,8 @@
       <c r="H5" s="1" t="n">
         <v>100000000000</v>
       </c>
-      <c r="I5" s="1" t="n">
-        <v>100000000000</v>
+      <c r="I5" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="J5" s="1" t="n">
         <v>4000000000</v>
@@ -1161,7 +1244,7 @@
         <v>1</v>
       </c>
       <c r="W5" s="1" t="n">
-        <v>50000000000000</v>
+        <v>300000000</v>
       </c>
       <c r="X5" s="1" t="n">
         <v>0</v>
@@ -1212,7 +1295,7 @@
         <v>0</v>
       </c>
       <c r="AO5" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AQ5" s="1" t="n">
         <v>0.275</v>
@@ -1238,7 +1321,7 @@
         <v>517</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>100000000000</v>
@@ -1298,7 +1381,7 @@
         <v>1</v>
       </c>
       <c r="W6" s="1" t="n">
-        <v>50000000000000</v>
+        <v>300000000</v>
       </c>
       <c r="X6" s="1" t="n">
         <v>0</v>
@@ -1349,7 +1432,7 @@
         <v>0</v>
       </c>
       <c r="AO6" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AQ6" s="1" t="n">
         <v>0.275</v>
@@ -1372,7 +1455,7 @@
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>100000000000</v>
@@ -1432,7 +1515,7 @@
         <v>1</v>
       </c>
       <c r="W7" s="1" t="n">
-        <v>20000000000000</v>
+        <v>175000000</v>
       </c>
       <c r="X7" s="1" t="n">
         <v>0</v>
@@ -1483,7 +1566,7 @@
         <v>0</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AQ7" s="1" t="n">
         <v>0.6</v>

--- a/resources/data-imports/Monsters/raid-bosses.xlsx
+++ b/resources/data-imports/Monsters/raid-bosses.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="64">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -200,9 +200,6 @@
   </si>
   <si>
     <t xml:space="preserve">Jester of Time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delusinal</t>
   </si>
   <si>
     <t xml:space="preserve">Delusional Memories</t>
@@ -224,7 +221,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -245,18 +242,6 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="6.4"/>
-      <color rgb="FF2E3436"/>
-      <name val="Adwaita Sans"/>
       <family val="0"/>
     </font>
   </fonts>
@@ -302,7 +287,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -311,11 +296,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -328,66 +309,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF2E3436"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -1204,8 +1125,8 @@
       <c r="H5" s="1" t="n">
         <v>100000000000</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>60</v>
+      <c r="I5" s="1" t="n">
+        <v>100000000000</v>
       </c>
       <c r="J5" s="1" t="n">
         <v>4000000000</v>
@@ -1295,7 +1216,7 @@
         <v>0</v>
       </c>
       <c r="AO5" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AQ5" s="1" t="n">
         <v>0.275</v>
@@ -1321,7 +1242,7 @@
         <v>517</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>100000000000</v>
@@ -1432,7 +1353,7 @@
         <v>0</v>
       </c>
       <c r="AO6" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AQ6" s="1" t="n">
         <v>0.275</v>
@@ -1455,7 +1376,7 @@
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>100000000000</v>
@@ -1566,7 +1487,7 @@
         <v>0</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AQ7" s="1" t="n">
         <v>0.6</v>
